--- a/EKG_Kalite_Yönetim_Sistemi/04_Parça ve Proses Kontrolü/04_Laboratuvar, COP ve Test Kapsamı/EKG-KLT-FRM-38_ece_r43_parcalanma_test_raporu__alternatif_duzen.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/04_Parça ve Proses Kontrolü/04_Laboratuvar, COP ve Test Kapsamı/EKG-KLT-FRM-38_ece_r43_parcalanma_test_raporu__alternatif_duzen.xlsx
@@ -1524,7 +1524,8 @@
   <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-38&amp;C&amp;"Arial,Regular"&amp;11ECE R43 Parçalanma Test Raporu - Alternatif Düzen</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 21.09.2026
+Revizyon nedeni: Geçmiş test sonucu ve kişi bilgileri aynen korunarak rapora teknik inceleme gereği eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
